--- a/lessons/indicators/The AutoTune filter/opt_results_RTS_1h_07-05-26 18-33_final_4_years.xlsx
+++ b/lessons/indicators/The AutoTune filter/opt_results_RTS_1h_07-05-26 18-33_final_4_years.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bt\PycharmProjects\Lessons\lessons\indicators\The AutoTune filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EACE1AE5-690D-4D39-B4C0-4DBA5C53EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89587B6-B613-41D6-9CD1-D2459C46B242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32196" yWindow="2424" windowWidth="29652" windowHeight="13788" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="264" yWindow="1608" windowWidth="29652" windowHeight="13788" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="by Contacts" sheetId="1" r:id="rId1"/>
@@ -29709,6 +29709,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
